--- a/results/link-prediction-gcn/Link/1shot/PTC_MR/GCN_total_results.xlsx
+++ b/results/link-prediction-gcn/Link/1shot/PTC_MR/GCN_total_results.xlsx
@@ -893,457 +893,457 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>0.4031±0.0000</t>
+          <t>0.4021±0.0007</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>0.5998±0.0000</t>
+          <t>0.5976±0.0006</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5962±0.0015</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5763±0.0277</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.5968±0.0087</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5899±0.0079</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5712±0.0399</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.5924±0.0000</t>
+          <t>0.5524±0.0197</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.5924±0.0000</t>
+          <t>0.5524±0.0197</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0.5924±0.0000</t>
+          <t>0.5524±0.0197</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.5960±0.0032</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.5213±0.0000</t>
+          <t>0.5065±0.0185</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>0.5799±0.0000</t>
+          <t>0.5744±0.0321</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>0.4031±0.0000</t>
+          <t>0.4021±0.0007</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5974±0.0013</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>0.5943±0.0000</t>
+          <t>0.5858±0.0169</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5554±0.0161</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5988±0.0009</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>0.5780±0.0000</t>
+          <t>0.5409±0.0305</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5974±0.0013</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5974±0.0013</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5974±0.0013</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5974±0.0013</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5757±0.0331</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5057±0.0041</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5974±0.0013</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>0.4031±0.0000</t>
+          <t>0.4021±0.0007</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>0.5948±0.0000</t>
+          <t>0.5885±0.0123</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5887±0.0089</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5962±0.0030</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5758±0.0274</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5799±0.0114</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5981±0.0003</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>0.5913±0.0000</t>
+          <t>0.5955±0.0017</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.5913±0.0000</t>
+          <t>0.5955±0.0017</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>0.5913±0.0000</t>
+          <t>0.5955±0.0017</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.5860±0.0000</t>
+          <t>0.5981±0.0003</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>0.5355±0.0000</t>
+          <t>0.5311±0.0070</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>0.5948±0.0000</t>
+          <t>0.5977±0.0015</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.4031±0.0000</t>
+          <t>0.4021±0.0007</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.5462±0.0000</t>
+          <t>0.5903±0.0350</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.5733±0.0000</t>
+          <t>0.5706±0.0190</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>0.5697±0.0000</t>
+          <t>0.5617±0.0086</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.5795±0.0000</t>
+          <t>0.5915±0.0089</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>0.5760±0.0000</t>
+          <t>0.5631±0.0391</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>0.5307±0.0000</t>
+          <t>0.5516±0.0342</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5484±0.0036</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5484±0.0036</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.5190±0.0000</t>
+          <t>0.5484±0.0036</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.5273±0.0000</t>
+          <t>0.5318±0.0305</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.5118±0.0000</t>
+          <t>0.5041±0.0055</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.5536±0.0000</t>
+          <t>0.5163±0.0175</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.4031±0.0000</t>
+          <t>0.4021±0.0007</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.5974±0.0009</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>0.5931±0.0000</t>
+          <t>0.5906±0.0106</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5731±0.0434</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.5985±0.0008</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5965±0.0003</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>0.5976±0.0000</t>
+          <t>0.5974±0.0013</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.6028±0.0031</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.6028±0.0031</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.6028±0.0031</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5865±0.0138</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.5177±0.0000</t>
+          <t>0.5219±0.0164</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5957±0.0005</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>0.4031±0.0000</t>
+          <t>0.4021±0.0007</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.5979±0.0003</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.5955±0.0000</t>
+          <t>0.5945±0.0034</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5964±0.0027</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.5955±0.0000</t>
+          <t>0.5942±0.0076</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5753±0.0162</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5983±0.0005</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.5794±0.0000</t>
+          <t>0.5983±0.0030</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>0.5794±0.0000</t>
+          <t>0.5983±0.0030</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>0.5794±0.0000</t>
+          <t>0.5983±0.0030</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.5974±0.0013</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.5379±0.0000</t>
+          <t>0.5101±0.0132</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
         <is>
-          <t>0.5314±0.0000</t>
+          <t>0.5961±0.0016</t>
         </is>
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.4031±0.0000</t>
+          <t>0.4021±0.0007</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>0.5147±0.0000</t>
+          <t>0.5064±0.0152</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>0.5343±0.0000</t>
+          <t>0.5697±0.0102</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.4740±0.0000</t>
+          <t>0.5419±0.0092</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.5733±0.0000</t>
+          <t>0.5663±0.0187</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.5453±0.0000</t>
+          <t>0.5797±0.0222</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.5291±0.0000</t>
+          <t>0.5099±0.0044</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.5166±0.0000</t>
+          <t>0.5079±0.0144</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.5166±0.0000</t>
+          <t>0.5079±0.0144</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.5166±0.0000</t>
+          <t>0.5079±0.0144</t>
         </is>
       </c>
       <c r="CL2" t="inlineStr">
         <is>
-          <t>0.5300±0.0000</t>
+          <t>0.5105±0.0150</t>
         </is>
       </c>
       <c r="CM2" t="inlineStr">
         <is>
-          <t>0.5047±0.0000</t>
+          <t>0.5026±0.0155</t>
         </is>
       </c>
       <c r="CN2" t="inlineStr">
         <is>
-          <t>0.5301±0.0000</t>
+          <t>0.5106±0.0042</t>
         </is>
       </c>
     </row>
@@ -1360,62 +1360,62 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>0.7498±0.0000</t>
+          <t>0.7481±0.0005</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7467±0.0016</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.7472±0.0000</t>
+          <t>0.7214±0.0329</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7449±0.0047</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7390±0.0074</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.6952±0.0769</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.7437±0.0000</t>
+          <t>0.6608±0.0510</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.7437±0.0000</t>
+          <t>0.6608±0.0510</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.7437±0.0000</t>
+          <t>0.6608±0.0510</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7342±0.0201</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.6196±0.0000</t>
+          <t>0.5981±0.0277</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>0.7337±0.0000</t>
+          <t>0.7062±0.0505</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1425,62 +1425,62 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7480±0.0010</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.7452±0.0000</t>
+          <t>0.7357±0.0170</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7091±0.0164</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7491±0.0007</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.7322±0.0000</t>
+          <t>0.6545±0.0649</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7480±0.0010</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7480±0.0010</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7480±0.0010</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7480±0.0010</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7169±0.0459</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>0.7487±0.0000</t>
+          <t>0.5957±0.0044</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7480±0.0010</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1490,62 +1490,62 @@
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.7459±0.0000</t>
+          <t>0.7399±0.0112</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7408±0.0072</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7467±0.0029</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7284±0.0246</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7324±0.0102</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7485±0.0003</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>0.7432±0.0000</t>
+          <t>0.7457±0.0022</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.7432±0.0000</t>
+          <t>0.7457±0.0022</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.7432±0.0000</t>
+          <t>0.7457±0.0022</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.7354±0.0000</t>
+          <t>0.7485±0.0003</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0.6179±0.0000</t>
+          <t>0.6619±0.0080</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>0.7459±0.0000</t>
+          <t>0.7481±0.0010</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
@@ -1555,62 +1555,62 @@
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>0.6879±0.0000</t>
+          <t>0.7096±0.0270</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.7267±0.0000</t>
+          <t>0.7239±0.0169</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>0.7247±0.0000</t>
+          <t>0.7160±0.0078</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>0.7322±0.0000</t>
+          <t>0.7430±0.0074</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.7289±0.0000</t>
+          <t>0.7139±0.0390</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6749±0.0242</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.6611±0.0000</t>
+          <t>0.6901±0.0043</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>0.6611±0.0000</t>
+          <t>0.6901±0.0043</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>0.6611±0.0000</t>
+          <t>0.6901±0.0043</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>0.6539±0.0000</t>
+          <t>0.6644±0.0342</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>0.5977±0.0000</t>
+          <t>0.5819±0.0099</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.6769±0.0000</t>
+          <t>0.6502±0.0093</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
@@ -1620,62 +1620,62 @@
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7480±0.0007</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>0.7446±0.0000</t>
+          <t>0.7373±0.0159</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7190±0.0359</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7487±0.0005</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7470±0.0002</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>0.7481±0.0000</t>
+          <t>0.7480±0.0010</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7442±0.0072</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7442±0.0072</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7442±0.0072</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7385±0.0119</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.6264±0.0000</t>
+          <t>0.6250±0.0101</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7462±0.0004</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
@@ -1685,62 +1685,62 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.7470±0.0000</t>
+          <t>0.7483±0.0003</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.7457±0.0026</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7467±0.0028</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.7465±0.0000</t>
+          <t>0.7449±0.0068</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.7476±0.0000</t>
+          <t>0.7261±0.0170</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7474±0.0015</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.7313±0.0000</t>
+          <t>0.7449±0.0028</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.7313±0.0000</t>
+          <t>0.7449±0.0028</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.7313±0.0000</t>
+          <t>0.7449±0.0028</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>0.7493±0.0000</t>
+          <t>0.7480±0.0010</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.6341±0.0000</t>
+          <t>0.5984±0.0245</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
         <is>
-          <t>0.6877±0.0000</t>
+          <t>0.7442±0.0047</t>
         </is>
       </c>
       <c r="CB3" t="inlineStr">
@@ -1750,62 +1750,62 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.6485±0.0000</t>
+          <t>0.6440±0.0136</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>0.6907±0.0000</t>
+          <t>0.7247±0.0083</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>0.6100±0.0000</t>
+          <t>0.6909±0.0080</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>0.7271±0.0000</t>
+          <t>0.7150±0.0186</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.7003±0.0000</t>
+          <t>0.6955±0.0455</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.6621±0.0000</t>
+          <t>0.6465±0.0050</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6456±0.0151</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6456±0.0151</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>0.6571±0.0000</t>
+          <t>0.6456±0.0151</t>
         </is>
       </c>
       <c r="CL3" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6466±0.0134</t>
         </is>
       </c>
       <c r="CM3" t="inlineStr">
         <is>
-          <t>0.6057±0.0000</t>
+          <t>0.5723±0.0100</t>
         </is>
       </c>
       <c r="CN3" t="inlineStr">
         <is>
-          <t>0.6655±0.0000</t>
+          <t>0.6475±0.0069</t>
         </is>
       </c>
     </row>
@@ -1817,457 +1817,457 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.7356±0.0000</t>
+          <t>0.6341±0.0760</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>0.5461±0.0000</t>
+          <t>0.6163±0.0466</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.4945±0.0000</t>
+          <t>0.4683±0.0343</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.3763±0.0000</t>
+          <t>0.6283±0.0506</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.4524±0.0000</t>
+          <t>0.5084±0.0100</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.5069±0.0000</t>
+          <t>0.5218±0.0273</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.5485±0.0000</t>
+          <t>0.5531±0.0449</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.5133±0.0000</t>
+          <t>0.5162±0.0120</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.5133±0.0000</t>
+          <t>0.5162±0.0120</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.5133±0.0000</t>
+          <t>0.5162±0.0120</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.5103±0.0000</t>
+          <t>0.5426±0.0427</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.4825±0.0000</t>
+          <t>0.4727±0.0154</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.5150±0.0000</t>
+          <t>0.5816±0.0311</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>0.6755±0.0000</t>
+          <t>0.6990±0.0064</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.5826±0.0000</t>
+          <t>0.5945±0.0114</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>0.4797±0.0000</t>
+          <t>0.5325±0.0704</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.4717±0.0000</t>
+          <t>0.4812±0.0841</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.4797±0.0000</t>
+          <t>0.5321±0.0520</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.5492±0.0000</t>
+          <t>0.4921±0.0290</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>0.6136±0.0000</t>
+          <t>0.5840±0.0099</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>0.6063±0.0000</t>
+          <t>0.5923±0.0115</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.6063±0.0000</t>
+          <t>0.5923±0.0115</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.6063±0.0000</t>
+          <t>0.5923±0.0115</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.5737±0.0000</t>
+          <t>0.5644±0.0174</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.4787±0.0000</t>
+          <t>0.4699±0.0123</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.6160±0.0000</t>
+          <t>0.6041±0.0111</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.6962±0.0000</t>
+          <t>0.6803±0.0154</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>0.6168±0.0000</t>
+          <t>0.5233±0.0130</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>0.4850±0.0000</t>
+          <t>0.4912±0.0068</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.4990±0.0009</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.4976±0.0000</t>
+          <t>0.5372±0.0563</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.5787±0.0000</t>
+          <t>0.5131±0.0177</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.5610±0.0000</t>
+          <t>0.5187±0.0055</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>0.5516±0.0000</t>
+          <t>0.5061±0.0337</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.5516±0.0000</t>
+          <t>0.5061±0.0337</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>0.5515±0.0000</t>
+          <t>0.5061±0.0337</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>0.5191±0.0000</t>
+          <t>0.5330±0.0140</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.4822±0.0000</t>
+          <t>0.4514±0.0020</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.5670±0.0000</t>
+          <t>0.5282±0.0036</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>0.6284±0.0000</t>
+          <t>0.6698±0.0064</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>0.5008±0.0000</t>
+          <t>0.5702±0.0333</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.4826±0.0000</t>
+          <t>0.4797±0.0134</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>0.4240±0.0000</t>
+          <t>0.5447±0.0579</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.4800±0.0000</t>
+          <t>0.5312±0.0224</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.5110±0.0000</t>
+          <t>0.5128±0.0256</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>0.4769±0.0000</t>
+          <t>0.5585±0.0164</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.4793±0.0000</t>
+          <t>0.4960±0.0218</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.4793±0.0000</t>
+          <t>0.4960±0.0218</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.4793±0.0000</t>
+          <t>0.4960±0.0218</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.4791±0.0000</t>
+          <t>0.4877±0.0341</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.4739±0.0000</t>
+          <t>0.4902±0.0025</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>0.4537±0.0000</t>
+          <t>0.4875±0.0048</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>0.7544±0.0000</t>
+          <t>0.6710±0.0725</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>0.5777±0.0000</t>
+          <t>0.5758±0.0229</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.4941±0.0000</t>
+          <t>0.5079±0.0172</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>0.4941±0.0000</t>
+          <t>0.6512±0.0272</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>0.5913±0.0000</t>
+          <t>0.5690±0.0554</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.5800±0.0000</t>
+          <t>0.5705±0.0189</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>0.5960±0.0000</t>
+          <t>0.5956±0.0138</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.4959±0.0000</t>
+          <t>0.5616±0.0136</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>0.4959±0.0000</t>
+          <t>0.5616±0.0136</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>0.4959±0.0000</t>
+          <t>0.5616±0.0136</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.5444±0.0000</t>
+          <t>0.5441±0.0210</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>0.4794±0.0000</t>
+          <t>0.4841±0.0194</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>0.5203±0.0000</t>
+          <t>0.5599±0.0235</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.7082±0.0000</t>
+          <t>0.6710±0.0557</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.5371±0.0000</t>
+          <t>0.5894±0.0177</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>0.4965±0.0000</t>
+          <t>0.4755±0.0185</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>0.5000±0.0000</t>
+          <t>0.5629±0.0929</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.5722±0.0000</t>
+          <t>0.5988±0.0497</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.5273±0.0000</t>
+          <t>0.5109±0.0214</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.5811±0.0000</t>
+          <t>0.5593±0.0310</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.5088±0.0000</t>
+          <t>0.5237±0.0159</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.5088±0.0000</t>
+          <t>0.5237±0.0159</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.5088±0.0000</t>
+          <t>0.5237±0.0159</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.5690±0.0000</t>
+          <t>0.5462±0.0119</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.4980±0.0000</t>
+          <t>0.4879±0.0112</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
         <is>
-          <t>0.5372±0.0000</t>
+          <t>0.5488±0.0120</t>
         </is>
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>0.7226±0.0000</t>
+          <t>0.6886±0.0131</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>0.4934±0.0000</t>
+          <t>0.4775±0.0145</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.4508±0.0000</t>
+          <t>0.4602±0.0148</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.4208±0.0000</t>
+          <t>0.4986±0.0934</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.4555±0.0000</t>
+          <t>0.4640±0.0245</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>0.5278±0.0000</t>
+          <t>0.4918±0.0180</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>0.5085±0.0000</t>
+          <t>0.4776±0.0130</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.4886±0.0000</t>
+          <t>0.4784±0.0063</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>0.4886±0.0000</t>
+          <t>0.4784±0.0063</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>0.4886±0.0000</t>
+          <t>0.4784±0.0063</t>
         </is>
       </c>
       <c r="CL4" t="inlineStr">
         <is>
-          <t>0.4874±0.0000</t>
+          <t>0.4714±0.0031</t>
         </is>
       </c>
       <c r="CM4" t="inlineStr">
         <is>
-          <t>0.4731±0.0000</t>
+          <t>0.4867±0.0091</t>
         </is>
       </c>
       <c r="CN4" t="inlineStr">
         <is>
-          <t>0.5389±0.0000</t>
+          <t>0.5065±0.0125</t>
         </is>
       </c>
     </row>
@@ -2279,457 +2279,457 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.7717±0.0000</t>
+          <t>0.6873±0.0535</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.6452±0.0000</t>
+          <t>0.6843±0.0412</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.5964±0.0000</t>
+          <t>0.5814±0.0188</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.5335±0.0000</t>
+          <t>0.7285±0.0316</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.5672±0.0000</t>
+          <t>0.6049±0.0258</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>0.6588±0.0000</t>
+          <t>0.6101±0.0187</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.6642±0.0000</t>
+          <t>0.6374±0.0485</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.5990±0.0000</t>
+          <t>0.5920±0.0164</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.5990±0.0000</t>
+          <t>0.5920±0.0164</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>0.5990±0.0000</t>
+          <t>0.5920±0.0164</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.6042±0.0000</t>
+          <t>0.6310±0.0550</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.5872±0.0000</t>
+          <t>0.5800±0.0031</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.6230±0.0000</t>
+          <t>0.6718±0.0197</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>0.7253±0.0000</t>
+          <t>0.7483±0.0063</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.6405±0.0000</t>
+          <t>0.6573±0.0083</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>0.5892±0.0000</t>
+          <t>0.6381±0.0656</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.5839±0.0000</t>
+          <t>0.6263±0.0704</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>0.5852±0.0000</t>
+          <t>0.6341±0.0371</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>0.6830±0.0000</t>
+          <t>0.5758±0.0255</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.6540±0.0000</t>
+          <t>0.6519±0.0122</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>0.6577±0.0000</t>
+          <t>0.6554±0.0080</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.6577±0.0000</t>
+          <t>0.6554±0.0080</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.6577±0.0000</t>
+          <t>0.6555±0.0081</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.6352±0.0000</t>
+          <t>0.6577±0.0178</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.5873±0.0000</t>
+          <t>0.5766±0.0109</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.6654±0.0000</t>
+          <t>0.6644±0.0077</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>0.7243±0.0000</t>
+          <t>0.7405±0.0098</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.6490±0.0000</t>
+          <t>0.5976±0.0131</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.5897±0.0000</t>
+          <t>0.5932±0.0037</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.5969±0.0000</t>
+          <t>0.5969±0.0017</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.6331±0.0000</t>
+          <t>0.6255±0.0544</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.6575±0.0000</t>
+          <t>0.6157±0.0150</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.6257±0.0000</t>
+          <t>0.6030±0.0054</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>0.6363±0.0000</t>
+          <t>0.5983±0.0264</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.6364±0.0000</t>
+          <t>0.5983±0.0264</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.6364±0.0000</t>
+          <t>0.5983±0.0264</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>0.5975±0.0000</t>
+          <t>0.6013±0.0048</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>0.5819±0.0000</t>
+          <t>0.5677±0.0051</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>0.6456±0.0000</t>
+          <t>0.6085±0.0024</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.7055±0.0000</t>
+          <t>0.7596±0.0117</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>0.6103±0.0000</t>
+          <t>0.6568±0.0460</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>0.5887±0.0000</t>
+          <t>0.5874±0.0072</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.5594±0.0000</t>
+          <t>0.6680±0.0638</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.6065±0.0000</t>
+          <t>0.6307±0.0155</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.6267±0.0000</t>
+          <t>0.6094±0.0425</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.5858±0.0000</t>
+          <t>0.6603±0.0222</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.5853±0.0000</t>
+          <t>0.6052±0.0141</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.5853±0.0000</t>
+          <t>0.6052±0.0141</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.5853±0.0000</t>
+          <t>0.6052±0.0141</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.5906±0.0000</t>
+          <t>0.6087±0.0301</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>0.5821±0.0000</t>
+          <t>0.5907±0.0028</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.5567±0.0000</t>
+          <t>0.6038±0.0038</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>0.7890±0.0000</t>
+          <t>0.7196±0.0538</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>0.6336±0.0000</t>
+          <t>0.6504±0.0202</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.6170±0.0298</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>0.5962±0.0000</t>
+          <t>0.7458±0.0116</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>0.6748±0.0000</t>
+          <t>0.6500±0.0409</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>0.6573±0.0000</t>
+          <t>0.6444±0.0192</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>0.6581±0.0000</t>
+          <t>0.6535±0.0146</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>0.6463±0.0000</t>
+          <t>0.6496±0.0196</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>0.6463±0.0000</t>
+          <t>0.6496±0.0196</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.6463±0.0000</t>
+          <t>0.6496±0.0196</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.6215±0.0000</t>
+          <t>0.6482±0.0046</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.5795±0.0000</t>
+          <t>0.5862±0.0115</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>0.6338±0.0000</t>
+          <t>0.6514±0.0231</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>0.7472±0.0000</t>
+          <t>0.7262±0.0323</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.6088±0.0000</t>
+          <t>0.6512±0.0066</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.5938±0.0000</t>
+          <t>0.5856±0.0097</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.5991±0.0000</t>
+          <t>0.6546±0.0814</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.6366±0.0000</t>
+          <t>0.6773±0.0501</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.6516±0.0000</t>
+          <t>0.6154±0.0310</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.6624±0.0000</t>
+          <t>0.6308±0.0297</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.5913±0.0000</t>
+          <t>0.6189±0.0311</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.5913±0.0000</t>
+          <t>0.6189±0.0311</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>0.5913±0.0000</t>
+          <t>0.6189±0.0312</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.6448±0.0000</t>
+          <t>0.6386±0.0169</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>0.6010±0.0000</t>
+          <t>0.5922±0.0053</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
         <is>
-          <t>0.6681±0.0000</t>
+          <t>0.6486±0.0115</t>
         </is>
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>0.7830±0.0000</t>
+          <t>0.7713±0.0156</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.5983±0.0000</t>
+          <t>0.5932±0.0089</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>0.5733±0.0000</t>
+          <t>0.5787±0.0074</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.5586±0.0000</t>
+          <t>0.6377±0.0808</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.5366±0.0000</t>
+          <t>0.5792±0.0337</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.6082±0.0000</t>
+          <t>0.5620±0.0139</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.6053±0.0000</t>
+          <t>0.5943±0.0171</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.5976±0.0109</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.5976±0.0109</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.5953±0.0000</t>
+          <t>0.5976±0.0109</t>
         </is>
       </c>
       <c r="CL5" t="inlineStr">
         <is>
-          <t>0.5936±0.0000</t>
+          <t>0.5868±0.0064</t>
         </is>
       </c>
       <c r="CM5" t="inlineStr">
         <is>
-          <t>0.5819±0.0000</t>
+          <t>0.5961±0.0057</t>
         </is>
       </c>
       <c r="CN5" t="inlineStr">
         <is>
-          <t>0.6388±0.0000</t>
+          <t>0.6195±0.0084</t>
         </is>
       </c>
     </row>
